--- a/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
+++ b/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">CGI-ISO-001 — ISO/IEC 27001:2022 Readiness Assessment &amp; Statement of Applicability</t>
   </si>
   <si>
-    <t xml:space="preserve">FICTIONAL DATA - Cypher Group Inc. is not a real company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Olugboye.</t>
+    <t xml:space="preserve">SIMULATED CASE STUDY - Cypher Group Inc. is a simulated company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Olugboye.</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Readiness assessment and 93-control Statement of Applicability for Cypher Group Inc., tracing every control to CGI-RSK-001 v1.1, CGI-GAP-001 and CGI-TPR-001.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional-data notice</t>
+    <t xml:space="preserve">Case-study notice</t>
   </si>
   <si>
     <t xml:space="preserve">All organisations, people, findings, scores, dates and costs are invented for a portfolio. Real product names are stand-ins; any assurance status attributed to them is invented. ISO wording is paraphrased.</t>
@@ -3940,7 +3940,7 @@
     <t xml:space="preserve">Target dates all after 16 Sep 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional-data notice on every sheet</t>
+    <t xml:space="preserve">Case-study notice on every sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Row 2 of every sheet</t>

--- a/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
+++ b/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
@@ -109,13 +109,13 @@
     <t xml:space="preserve">Partial / condition</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub upload</t>
+    <t xml:space="preserve">CodeCo upload</t>
   </si>
   <si>
     <t xml:space="preserve">Folder 05-iso27001-readiness-soa/ : this workbook, the .md, the .csv and data/*.csv. Create folders by typing the path in the file-name box (for example 05-iso27001-readiness-soa/data/05-clause-readiness.csv).</t>
   </si>
   <si>
-    <t xml:space="preserve">Notion upload</t>
+    <t xml:space="preserve">WikiCo upload</t>
   </si>
   <si>
     <t xml:space="preserve">Import the CSVs, not this workbook: Settings &gt; Import &gt; CSV. Set Theme, Applicable, Status and Owner to Select; Maturity to Number.</t>
@@ -160,13 +160,13 @@
     <t xml:space="preserve">Head office (ISO-A01); remote and home working under CGI-POL-001 section 4.4</t>
   </si>
   <si>
-    <t xml:space="preserve">No data centre operated; production physical controls are AWS's, assured through A.5.23</t>
+    <t xml:space="preserve">No data centre operated; production physical controls are CloudCo's, assured through A.5.23</t>
   </si>
   <si>
     <t xml:space="preserve">Technology</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS production (eu-central-1; backups us-east-1); GitHub; Google Workspace (IdP); Slack; Auth0; Datadog; Stripe integration; BYOD endpoints accessing company data</t>
+    <t xml:space="preserve">CloudCo production (eu-central-1; backups us-east-1); CodeCo; OfficeCo (IdP); ChatCo; LoginCo; MonitorCo; PaymentsCo integration; BYOD endpoints accessing company data</t>
   </si>
   <si>
     <t xml:space="preserve">Vendors' internal controls - managed as interfaces through A.5.19-A.5.23 and CGI-TPR-001</t>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">Interfaces (4.3 c)</t>
   </si>
   <si>
-    <t xml:space="preserve">17 vendors CGI-VEN-001 to -017 (Tier 1/2/3 = 7/6/4); AWS shared-responsibility boundary (ISO-02)</t>
+    <t xml:space="preserve">17 vendors CGI-VEN-001 to -017 (Tier 1/2/3 = 7/6/4); CloudCo shared-responsibility boundary (ISO-02)</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -352,7 +352,7 @@
     <t xml:space="preserve">Policy approval is segregated (CGI-POL-002 approver moved to the CEO), but engineers can commit straight to production with no second person, which is the code-path duty conflict behind R-004.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: CGI-POL-002 approval record. Required: segregation-of-duties matrix; GitHub branch protection requiring a second reviewer.</t>
+    <t xml:space="preserve">Held: CGI-POL-002 approval record. Required: segregation-of-duties matrix; CodeCo branch protection requiring a second reviewer.</t>
   </si>
   <si>
     <t xml:space="preserve">Chief Technology Officer</t>
@@ -502,7 +502,7 @@
     <t xml:space="preserve">Inventory of information and other associated assets</t>
   </si>
   <si>
-    <t xml:space="preserve">ID.AM = 1. The CGI-TPR-001 vendor inventory is one input; no inventory of AWS data stores, repositories, drives or endpoints exists.</t>
+    <t xml:space="preserve">ID.AM = 1. The CGI-TPR-001 vendor inventory is one input; no inventory of CloudCo data stores, repositories, drives or endpoints exists.</t>
   </si>
   <si>
     <t xml:space="preserve">Held: CGI-TPR-001 vendor inventory (17 rows). Required: asset and SaaS inventory with owner and CGI-POL-004 label per asset.</t>
@@ -529,7 +529,7 @@
     <t xml:space="preserve">Acceptable use of information and other associated assets</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-001 is approved, including section 4.5 on AI use, but 40% of staff have not acknowledged it and Otter.ai shows it being bypassed (VR-006).</t>
+    <t xml:space="preserve">CGI-POL-001 is approved, including section 4.5 on AI use, but 40% of staff have not acknowledged it and ScribeCo shows it being bypassed (VR-006).</t>
   </si>
   <si>
     <t xml:space="preserve">Held: CGI-POL-001 v1.0. Required: 100% acknowledgement; AI-use briefing record.</t>
@@ -544,7 +544,7 @@
     <t xml:space="preserve">ID.AM; GV.PO</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-VEN-012 Otter.ai used in breach of CGI-POL-001 section 4.5</t>
+    <t xml:space="preserve">CGI-VEN-012 ScribeCo used in breach of CGI-POL-001 section 4.5</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.11</t>
@@ -565,7 +565,7 @@
     <t xml:space="preserve">PR.AA</t>
   </si>
   <si>
-    <t xml:space="preserve">F-003 (no SCIM on Slack; leaver removal manual)</t>
+    <t xml:space="preserve">F-003 (no SCIM on ChatCo; leaver removal manual)</t>
   </si>
   <si>
     <t xml:space="preserve">ISO-11; REC-02</t>
@@ -601,7 +601,7 @@
     <t xml:space="preserve">No asset carries a classification label, so the Handling Matrix cannot be enforced (GAP-007).</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: labelling rules in CGI-POL-004. Required: labels applied in Google Workspace, repositories and data stores.</t>
+    <t xml:space="preserve">Held: labelling rules in CGI-POL-004. Required: labels applied in OfficeCo, repositories and data stores.</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.14</t>
@@ -652,10 +652,10 @@
     <t xml:space="preserve">Identity management</t>
   </si>
   <si>
-    <t xml:space="preserve">Google Workspace is the identity provider (VRA addendum step 3), but Slack, Notion, Grammarly and Miro are not federated, so identity lifecycle is incomplete.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held: CGI-POL-003 JML process. Required: SSO/SCIM on Tier 1 vendors (Slack by 15 Nov 2026); KRI-V5 at 100%.</t>
+    <t xml:space="preserve">OfficeCo is the identity provider (VRA addendum step 3), but ChatCo, WikiCo, WriteCo and WhiteboardCo are not federated, so identity lifecycle is incomplete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Held: CGI-POL-003 JML process. Required: SSO/SCIM on Tier 1 vendors (ChatCo by 15 Nov 2026); KRI-V5 at 100%.</t>
   </si>
   <si>
     <t xml:space="preserve">F-003; KRI-V5</t>
@@ -691,7 +691,7 @@
     <t xml:space="preserve">Access rights</t>
   </si>
   <si>
-    <t xml:space="preserve">The CGI-POL-003 section 4.7.1 quarterly privileged review is mandated but has never run; the AWS report assumes CGI performs this review (CUEC).</t>
+    <t xml:space="preserve">The CGI-POL-003 section 4.7.1 quarterly privileged review is mandated but has never run; the CloudCo report assumes CGI performs this review (CUEC).</t>
   </si>
   <si>
     <t xml:space="preserve">Held: CGI-POL-003 section 4.7.1. Required: dated, signed quarterly review records (four by Stage 2).</t>
@@ -763,7 +763,7 @@
     <t xml:space="preserve">Questionnaire domain 7 and clauses 4-5 design the ICT supply-chain control, but fourth parties behind carve-out reports have never been reconciled.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: CGI-TPR-002 VQ-33 to VQ-36. Required: CSOC reconciliation records for AWS and Slack.</t>
+    <t xml:space="preserve">Held: CGI-TPR-002 VQ-33 to VQ-36. Required: CSOC reconciliation records for CloudCo and ChatCo.</t>
   </si>
   <si>
     <t xml:space="preserve">VR-003; VR-004</t>
@@ -790,7 +790,7 @@
     <t xml:space="preserve">VR-003; VR-009</t>
   </si>
   <si>
-    <t xml:space="preserve">F-006 (stale Slack SOC 2); F-012 (sub-processor feed not subscribed)</t>
+    <t xml:space="preserve">F-006 (stale ChatCo SOC 2); F-012 (sub-processor feed not subscribed)</t>
   </si>
   <si>
     <t xml:space="preserve">VRA-2026-001 C2; REC-15</t>
@@ -802,7 +802,7 @@
     <t xml:space="preserve">Information security for use of cloud services</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud acquisition is covered by CGI-TPR-001, but there is no cloud-specific process, no documented shared-responsibility boundary and no tested exit, and the four CUECs are unaccepted, so the AWS opinion does not yet cover CGI's use.</t>
+    <t xml:space="preserve">Cloud acquisition is covered by CGI-TPR-001, but there is no cloud-specific process, no documented shared-responsibility boundary and no tested exit, and the four CUECs are unaccepted, so the CloudCo opinion does not yet cover CGI's use.</t>
   </si>
   <si>
     <t xml:space="preserve">Held: VRA-2026-001. Required: signed CUEC acceptance (C1); shared-responsibility statement; exit plan for Tier 1 cloud vendors (KRI-V7).</t>
@@ -814,7 +814,7 @@
     <t xml:space="preserve">GV.SC; PR.IR</t>
   </si>
   <si>
-    <t xml:space="preserve">VRA-2026-001 AWS PASS WITH CONDITIONS (F-010 to F-013; all four conditions are CGI's)</t>
+    <t xml:space="preserve">VRA-2026-001 CloudCo PASS WITH CONDITIONS (F-010 to F-013; all four conditions are CGI's)</t>
   </si>
   <si>
     <t xml:space="preserve">15 Dec 2026</t>
@@ -934,7 +934,7 @@
     <t xml:space="preserve">R-003; R-004; VR-004</t>
   </si>
   <si>
-    <t xml:space="preserve">F-008 (no customer-accessible Slack audit log)</t>
+    <t xml:space="preserve">F-008 (no customer-accessible ChatCo audit log)</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.29</t>
@@ -943,10 +943,10 @@
     <t xml:space="preserve">Information security during disruption</t>
   </si>
   <si>
-    <t xml:space="preserve">There is no plan for maintaining security during disruption. Concentration means one AWS regional failure also removes monitoring, ticketing and runbooks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held: AWS snapshots only. Required: disruption plan naming the out-of-band tools; status page (CGI-VEN-017) live.</t>
+    <t xml:space="preserve">There is no plan for maintaining security during disruption. Concentration means one CloudCo regional failure also removes monitoring, ticketing and runbooks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Held: CloudCo snapshots only. Required: disruption plan naming the out-of-band tools; status page (CGI-VEN-017) live.</t>
   </si>
   <si>
     <t xml:space="preserve">R-002; VR-002</t>
@@ -955,7 +955,7 @@
     <t xml:space="preserve">RC.RP; RC.CO</t>
   </si>
   <si>
-    <t xml:space="preserve">VR-002 concentration: 5 vendors share AWS with the platform</t>
+    <t xml:space="preserve">VR-002 concentration: 5 vendors share CloudCo with the platform</t>
   </si>
   <si>
     <t xml:space="preserve">REC-03; REC-14</t>
@@ -973,7 +973,7 @@
     <t xml:space="preserve">Backups exist but have never been restored, and no RTO or RPO is declared (CG-01). CGI-RSK-001 gives R-002 no backup credit until this closes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: AWS native snapshots. Required: CGI-POL-006 with RTO/RPO; dated restore test report.</t>
+    <t xml:space="preserve">Held: CloudCo native snapshots. Required: CGI-POL-006 with RTO/RPO; dated restore test report.</t>
   </si>
   <si>
     <t xml:space="preserve">R-002; VR-002; VR-007</t>
@@ -1039,7 +1039,7 @@
     <t xml:space="preserve">R-003; VR-004</t>
   </si>
   <si>
-    <t xml:space="preserve">F-005 (Slack unlimited retention)</t>
+    <t xml:space="preserve">F-005 (ChatCo unlimited retention)</t>
   </si>
   <si>
     <t xml:space="preserve">REC-07; ISO-08</t>
@@ -1114,7 +1114,7 @@
     <t xml:space="preserve">Documented operating procedures</t>
   </si>
   <si>
-    <t xml:space="preserve">Policies exist, but the procedures beneath them do not (GAP-017, GAP-020), and the planned runbook location shares AWS with the platform.</t>
+    <t xml:space="preserve">Policies exist, but the procedures beneath them do not (GAP-017, GAP-020), and the planned runbook location shares CloudCo with the platform.</t>
   </si>
   <si>
     <t xml:space="preserve">Held: policy pack only. Required: runbooks, stored where they survive a platform outage.</t>
@@ -1123,7 +1123,7 @@
     <t xml:space="preserve">R-002; R-005; VR-002</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-VEN-011 Notion holds runbooks: no DPA, public links enabled, AWS-hosted</t>
+    <t xml:space="preserve">CGI-VEN-011 WikiCo holds runbooks: no DPA, public links enabled, CloudCo-hosted</t>
   </si>
   <si>
     <t xml:space="preserve">A.6.1</t>
@@ -1306,10 +1306,10 @@
     <t xml:space="preserve">Physical security monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">EXCLUDED. There are no secure areas or on-premises information processing facilities: production runs in AWS, whose physical monitoring is assured through A.5.23 (VRA-2026-001). The serviced office holds only portable endpoints. Re-include if servers, network equipment or Confidential paper records are kept on site.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held: VRA-2026-001 (AWS SOC 2 covers data-centre monitoring). Required: exclusion approved in SoA v1.0.</t>
+    <t xml:space="preserve">EXCLUDED. There are no secure areas or on-premises information processing facilities: production runs in CloudCo, whose physical monitoring is assured through A.5.23 (VRA-2026-001). The serviced office holds only portable endpoints. Re-include if servers, network equipment or Confidential paper records are kept on site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Held: VRA-2026-001 (CloudCo SOC 2 covers data-centre monitoring). Required: exclusion approved in SoA v1.0.</t>
   </si>
   <si>
     <t xml:space="preserve">N/A - re-evaluate at SoA review 30 Sep 2027</t>
@@ -1399,7 +1399,7 @@
     <t xml:space="preserve">Supporting utilities</t>
   </si>
   <si>
-    <t xml:space="preserve">EXCLUDED. No information processing facility is operated, so there are no utilities to protect. Power and cooling for production are AWS's responsibility, assured through A.5.23 (VRA-2026-001).</t>
+    <t xml:space="preserve">EXCLUDED. No information processing facility is operated, so there are no utilities to protect. Power and cooling for production are CloudCo's responsibility, assured through A.5.23 (VRA-2026-001).</t>
   </si>
   <si>
     <t xml:space="preserve">Held: VRA-2026-001. Required: exclusion approved in SoA v1.0.</t>
@@ -1465,7 +1465,7 @@
     <t xml:space="preserve">Privileged access rights</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-002 section 4.3.3 mandates phishing-resistant MFA for privileged accounts, but the CGI-POL-003 section 4.7.1 quarterly review has never run and the AWS root-account CUEC is unaccepted.</t>
+    <t xml:space="preserve">CGI-POL-002 section 4.3.3 mandates phishing-resistant MFA for privileged accounts, but the CGI-POL-003 section 4.7.1 quarterly review has never run and the CloudCo root-account CUEC is unaccepted.</t>
   </si>
   <si>
     <t xml:space="preserve">Held: CGI-POL-002 section 4.3.3. Required: privileged account list; quarterly review records; root MFA evidence.</t>
@@ -1510,7 +1510,7 @@
     <t xml:space="preserve">Held: CGI-POL-002 section 4.5.2 (fragment). Required: repository access review; branch protection configuration export.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-VEN-002 GitHub: Tier 1, inherent 15 Critical, no branch protection on the CGI side</t>
+    <t xml:space="preserve">CGI-VEN-002 CodeCo: Tier 1, inherent 15 Critical, no branch protection on the CGI side</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.5</t>
@@ -1525,7 +1525,7 @@
     <t xml:space="preserve">Held: CGI-TRK-001 (80%). Required: 100% enrolment export; phishing-resistant MFA on all admins.</t>
   </si>
   <si>
-    <t xml:space="preserve">F-003 (no SSO on Slack); F-010</t>
+    <t xml:space="preserve">F-003 (no SSO on ChatCo); F-010</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.6</t>
@@ -1582,10 +1582,10 @@
     <t xml:space="preserve">Configuration management</t>
   </si>
   <si>
-    <t xml:space="preserve">CG-03: there is no AWS configuration baseline and no drift detection (PR.IR = 0). This is the documented reason R-005 stays High.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held: none. Required: CIS AWS Foundations baseline; posture-monitoring reports.</t>
+    <t xml:space="preserve">CG-03: there is no CloudCo configuration baseline and no drift detection (PR.IR = 0). This is the documented reason R-005 stays High.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Held: none. Required: CIS CloudCo Foundations baseline; posture-monitoring reports.</t>
   </si>
   <si>
     <t xml:space="preserve">R-005; R-004</t>
@@ -1630,10 +1630,10 @@
     <t xml:space="preserve">There is no masking of customer data in logs or lower environments; Project 1's mapping to the Handling Matrix was weak and is not credited.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: none. Required: masking rule for logs and test data; Datadog scrubbing configuration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGI-VEN-007 Datadog: log scrubbing rules not verified</t>
+    <t xml:space="preserve">Held: none. Required: masking rule for logs and test data; MonitorCo scrubbing configuration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGI-VEN-007 MonitorCo: log scrubbing rules not verified</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.12</t>
@@ -1645,7 +1645,7 @@
     <t xml:space="preserve">CG-05: there is no data-loss prevention; monitoring is metadata-only.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: CGI-POL-001 section 4.5.2, a behavioural rule against entering Confidential data into unapproved AI tools (a fragment, not leakage prevention). Required: egress and DLP rules on Google Workspace and GitHub; alert samples.</t>
+    <t xml:space="preserve">Held: CGI-POL-001 section 4.5.2, a behavioural rule against entering Confidential data into unapproved AI tools (a fragment, not leakage prevention). Required: egress and DLP rules on OfficeCo and CodeCo; alert samples.</t>
   </si>
   <si>
     <t xml:space="preserve">PR.DS; DE.CM</t>
@@ -1669,7 +1669,7 @@
     <t xml:space="preserve">Seatbelt, not brakes: backup acts after the bang, limiting the impact of R-002 ransomware. Snapshots exist but have never been restored (CG-01), so no credit is taken.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: AWS snapshot configuration. Required: CGI-POL-006; dated restore test to a clean environment; six-monthly repeat.</t>
+    <t xml:space="preserve">Held: CloudCo snapshot configuration. Required: CGI-POL-006; dated restore test to a clean environment; six-monthly repeat.</t>
   </si>
   <si>
     <t xml:space="preserve">PR.IR; RC.RP</t>
@@ -1693,7 +1693,7 @@
     <t xml:space="preserve">Held: none. Required: availability architecture record (zones and regions); failover test.</t>
   </si>
   <si>
-    <t xml:space="preserve">VR-002; CGI-VEN-017 deliberately hosted off AWS</t>
+    <t xml:space="preserve">VR-002; CGI-VEN-017 deliberately hosted off CloudCo</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.15</t>
@@ -1702,10 +1702,10 @@
     <t xml:space="preserve">Logging</t>
   </si>
   <si>
-    <t xml:space="preserve">Some logs exist ad hoc (application logs in Datadog), but organisation-wide CloudTrail is unverified and there is no central security log or retention (DE.CM = 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held: Datadog APM (engineering use). Required: CloudTrail with validation; central log account; retention standard.</t>
+    <t xml:space="preserve">Some logs exist ad hoc (application logs in MonitorCo), but organisation-wide CloudTrail is unverified and there is no central security log or retention (DE.CM = 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Held: MonitorCo APM (engineering use). Required: CloudTrail with validation; central log account; retention standard.</t>
   </si>
   <si>
     <t xml:space="preserve">R-003; R-005; VR-004</t>
@@ -1936,7 +1936,7 @@
     <t xml:space="preserve">Outsourced development</t>
   </si>
   <si>
-    <t xml:space="preserve">EXCLUDED. All development is performed by CGI employees (assumption ISO-A02). Re-include before any contractor or agency writes code. Supplier assurance for development tools (GitHub) is covered by A.5.19 to A.5.22.</t>
+    <t xml:space="preserve">EXCLUDED. All development is performed by CGI employees (assumption ISO-A02). Re-include before any contractor or agency writes code. Supplier assurance for development tools (CodeCo) is covered by A.5.19 to A.5.22.</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.31</t>
@@ -3058,7 +3058,7 @@
     <t xml:space="preserve">Would support GV.OC 1 -&gt; 2 once approved</t>
   </si>
   <si>
-    <t xml:space="preserve">Approve the ISMS scope and boundary, including the AWS shared-responsibility statement</t>
+    <t xml:space="preserve">Approve the ISMS scope and boundary, including the CloudCo shared-responsibility statement</t>
   </si>
   <si>
     <t xml:space="preserve">4.3; A.5.23; A.8.27</t>
@@ -3397,7 +3397,7 @@
     <t xml:space="preserve">The REC-10 agenda (KRIs, scorecard, TP status) is not a full clause 9.3 review. Extend it to the 9.3.2 a) to g) inputs and minute it as the management review.</t>
   </si>
   <si>
-    <t xml:space="preserve">CIS AWS baseline; posture monitoring</t>
+    <t xml:space="preserve">CIS CloudCo baseline; posture monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Q2 2027</t>
@@ -3562,7 +3562,7 @@
     <t xml:space="preserve">REC-18 (Q4 2027) falls after Stage 2</t>
   </si>
   <si>
-    <t xml:space="preserve">The scope statement needs the AWS boundary now.</t>
+    <t xml:space="preserve">The scope statement needs the CloudCo boundary now.</t>
   </si>
   <si>
     <t xml:space="preserve">Split: documentation to ISO-02 (Oct 2026); segmentation remains Q4 2027 in the RTP.</t>
@@ -4575,125 +4575,185 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-ISO-001 — ISO/IEC 27001:2022 Readiness Assessment &amp; Statement of Applicability</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIMULATED CASE STUDY - Cypher Group Inc. is a simulated company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Olugboye.</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purpose</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Readiness assessment and 93-control Statement of Applicability for Cypher Group Inc., tracing every control to CGI-RSK-001 v1.1, CGI-GAP-001 and CGI-TPR-001.</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>7</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case-study notice</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All organisations, people, findings, scores, dates and costs are invented for a portfolio. ISO wording is paraphrased.</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>9</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheets</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01_Scope · 02_SoA · 03_SoA_Summary · 04_Clauses · 05_DocInfo · 06_Readiness · 07_Roadmap · 08_REC_Reconciliation · 09_GAP_Impact · 10_Assumptions · 11_Issue_Checklist · 12_Lists</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How status works</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02_SoA column N (maturity 0-4, yellow) drives column F (status, grey formula): 0 = Not started; 1-2 = Partial; 3-4 = Implemented; Applicable = N gives N/A - excluded. Column S checks maturity is not above the highest related CGI-GAP-001 Category score (09_GAP_Impact).</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>13</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How the score works</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06_Readiness: 0.6 x clause score (04_Clauses) + 0.4 x Annex A score (03_SoA_Summary). Any failed gate (04_Clauses column K) forces NO-GO.</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>15</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour legend - yellow</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input you may change (maturity, applicability, clause scores, weights, costs, document status)</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>17</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour legend - grey</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula - do not overwrite</t>
+        </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>19</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour legend - green</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass / met / implemented / worked example</t>
+        </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>21</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour legend - red</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail / absent / not started / zero</t>
+        </is>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>23</v>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour legend - amber</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial / condition</t>
+        </is>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>25</v>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitHub upload</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Folder 05-iso27001-readiness-soa/ : this workbook, the .md, the .csv and data/*.csv. Create folders by typing the path in the file-name box (for example 05-iso27001-readiness-soa/data/05-clause-readiness.csv).</t>
+        </is>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>27</v>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notion upload</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import the CSVs, not this workbook: Settings &gt; Import &gt; CSV. Set Theme, Applicable, Status and Owner to Select; Maturity to Number.</t>
+        </is>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>29</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verification</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recalculated in LibreOffice before delivery with zero formula errors; counts cross-checked in code (see 11_Issue_Checklist).</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
+++ b/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
@@ -1585,7 +1585,7 @@
     <t xml:space="preserve">CG-03: there is no CloudCo configuration baseline and no drift detection (PR.IR = 0). This is the documented reason R-005 stays High.</t>
   </si>
   <si>
-    <t xml:space="preserve">Held: none. Required: CIS CloudCo Foundations baseline; posture-monitoring reports.</t>
+    <t xml:space="preserve">Held: none. Required: CIS AWS Foundations baseline; posture-monitoring reports.</t>
   </si>
   <si>
     <t xml:space="preserve">R-005; R-004</t>
@@ -3397,7 +3397,7 @@
     <t xml:space="preserve">The REC-10 agenda (KRIs, scorecard, TP status) is not a full clause 9.3 review. Extend it to the 9.3.2 a) to g) inputs and minute it as the management review.</t>
   </si>
   <si>
-    <t xml:space="preserve">CIS CloudCo baseline; posture monitoring</t>
+    <t xml:space="preserve">CIS AWS baseline; posture monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Q2 2027</t>

--- a/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
+++ b/05-iso27001-readiness-soa/05-iso27001-readiness-and-soa.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">CGI-ISO-001 — ISO/IEC 27001:2022 Readiness Assessment &amp; Statement of Applicability</t>
   </si>
   <si>
-    <t xml:space="preserve">SIMULATED CASE STUDY - Cypher Group Inc. is a simulated company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Olugboye.</t>
+    <t xml:space="preserve">SIMULATED CASE STUDY - Cypher Group Inc. is a simulated company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Gold.</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -4584,7 +4584,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIMULATED CASE STUDY - Cypher Group Inc. is a simulated company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Olugboye.</t>
+          <t xml:space="preserve">SIMULATED CASE STUDY - Cypher Group Inc. is a simulated company. CGI-ISO-001 v1.0, 16 Sep 2026. Prepared by O.S; for approval by Jerry Gold.</t>
         </is>
       </c>
     </row>
